--- a/public/bulk-templates/Company-list-template.xlsx
+++ b/public/bulk-templates/Company-list-template.xlsx
@@ -1703,13 +1703,16 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showErrorMessage="1" errorTitle="Company Size" error="Choose Small, Medium, Large, or Enterprise." sqref="C2:C1000">
+      <formula1>"Small,Medium,Large,Enterprise"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showErrorMessage="1" errorTitle="Status" error="Choose Active or Inactive." sqref="P2:P1000">
+      <formula1>"Active,Inactive"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:P26"/>
   </ignoredErrors>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showErrorMessage="1" errorTitle="Company Size" error="Choose Small, Medium, Large, or Enterprise." sqref="C2:C1000">
-      <formula1>"Small,Medium,Large,Enterprise"</formula1>
-    </dataValidation>
-  </dataValidations>
 </worksheet>
 </file>